--- a/artfynd/A 1725-2022 artfynd.xlsx
+++ b/artfynd/A 1725-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1725-2022 artfynd.xlsx
+++ b/artfynd/A 1725-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7260696</v>
+        <v>7260702</v>
       </c>
       <c r="B2" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2671</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,10 +725,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>651335.7679283684</v>
+        <v>651265</v>
       </c>
       <c r="R2" t="n">
-        <v>6645982.805283895</v>
+        <v>6645936</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,26 +758,11 @@
           <t>2014-04-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-04-05</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>huvuddelen sitter SO-vänd</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -795,12 +779,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Block (&gt; 200 mm)</t>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Rock (&gt; 200 mm)</t>
+          <t>Wood surface of dead wood</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -818,61 +802,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7260698</v>
+        <v>55855274</v>
       </c>
       <c r="B3" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84160</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2671</v>
+        <v>1633</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Rökpipsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Urnula craterium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Schwein.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sjödyns gård, 1,1 km V-ut, Upl</t>
+          <t>Sjödyn 4,5 km S om Storvreta, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>651335.0511297911</v>
+        <v>651295</v>
       </c>
       <c r="R3" t="n">
-        <v>6645975.748950242</v>
+        <v>6645899</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,27 +876,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2014-04-05</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-05-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2014-04-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-05-05</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>sitter V-vänd</t>
+          <t>1 ex. på liggande, murken hasselved i medelåldrig blandskog med gran, ek och hassel, i svag sluttning med rörligt markvatten.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -933,43 +900,38 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Lövrik barrskog</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Block (&gt; 200 mm)</t>
+          <t>Medelåldrig blandskog med gran, ek och hassel.</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Hassel</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Rock (&gt; 200 mm)</t>
+          <t>Liggande, murken hasselved. # Hassel</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7260700</v>
+        <v>7260699</v>
       </c>
       <c r="B4" t="n">
-        <v>93158</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,29 +939,25 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2818</v>
+        <v>2667</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1007,10 +965,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>651273.4056646463</v>
+        <v>651321</v>
       </c>
       <c r="R4" t="n">
-        <v>6645934.076189821</v>
+        <v>6645945</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1040,19 +998,14 @@
           <t>2014-04-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2014-04-05</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>sitter O-vänd</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1071,12 +1024,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Vedyta på död ved</t>
+          <t>Block (&gt; 200 mm)</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood</t>
+          <t>Rock (&gt; 200 mm)</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1094,15 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96192146</v>
+        <v>96202688</v>
       </c>
       <c r="B5" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,44 +1058,45 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5964</v>
+        <v>2667</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sjödyn, 400 m NO om, Upl</t>
+          <t>Sjödyn, 200 m NNO om, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>651561.1628660103</v>
+        <v>651350</v>
       </c>
       <c r="R5" t="n">
-        <v>6645942.344381058</v>
+        <v>6645907</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1174,19 +1123,9 @@
           <t>2021-09-18</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-09-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1201,12 +1140,17 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Ängsgranskog</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Granskog med ett motionsspår där svampen växer i kanten av spåret.</t>
+          <t>Ängsblandskog</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Stone/rock on land # Flyttblock</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1228,15 +1172,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96202698</v>
+        <v>7260696</v>
       </c>
       <c r="B6" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1261,28 +1200,31 @@
           <t>(Hedw.) Brid.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sjödyn, 200 m NNO om, Upl</t>
+          <t>Sjödyns gård, 1,1 km V-ut, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>651349.9481455521</v>
+        <v>651336</v>
       </c>
       <c r="R6" t="n">
-        <v>6645906.589776047</v>
+        <v>6645983</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1306,22 +1248,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-09-18</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-04-05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-09-18</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-04-05</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>huvuddelen sitter SO-vänd</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1330,53 +1267,43 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Ängsblandskog</t>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Lövrik barrskog</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Sten/berg på land</t>
+          <t>Block (&gt; 200 mm)</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stone/rock on land # Flyttblock</t>
+          <t>Rock (&gt; 200 mm)</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Thorleif Joelson</t>
+          <t>Henry Åkerström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Thorleif Joelson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
-        </is>
-      </c>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96202688</v>
+        <v>7260698</v>
       </c>
       <c r="B7" t="n">
-        <v>93145</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,45 +1311,48 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neckera complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Huebener</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sjödyn, 200 m NNO om, Upl</t>
+          <t>Sjödyns gård, 1,1 km V-ut, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>651349.9481455521</v>
+        <v>651335</v>
       </c>
       <c r="R7" t="n">
-        <v>6645906.589776047</v>
+        <v>6645976</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1446,22 +1376,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-09-18</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-04-05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-09-18</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-04-05</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>sitter V-vänd</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1470,97 +1395,86 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Ängsblandskog</t>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Lövrik barrskog</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Sten/berg på land</t>
+          <t>Block (&gt; 200 mm)</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stone/rock on land # Flyttblock</t>
+          <t>Rock (&gt; 200 mm)</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Thorleif Joelson</t>
+          <t>Henry Åkerström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Thorleif Joelson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
-        </is>
-      </c>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>74636550</v>
+        <v>96202698</v>
       </c>
       <c r="B8" t="n">
-        <v>55608</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>2671</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sjödyn 4,5 km S om Storvreta, Upl</t>
+          <t>Sjödyn, 200 m NNO om, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>651411.5851075813</v>
+        <v>651350</v>
       </c>
       <c r="R8" t="n">
-        <v>6645911.622456951</v>
+        <v>6645907</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1587,22 +1501,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2006-05-05</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2006-05-05</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1611,21 +1515,578 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Ängsblandskog</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Stone/rock on land # Flyttblock</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7260700</v>
+      </c>
+      <c r="B9" t="n">
+        <v>96458</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sjödyns gård, 1,1 km V-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>651273</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6645934</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Vaksala</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2014-04-05</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2014-04-05</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Lövrik barrskog</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>96192146</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sjödyn, 400 m NO om, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>651561</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6645942</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Vaksala</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2021-09-18</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2021-09-18</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Ängsgranskog</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Granskog med ett motionsspår där svampen växer i kanten av spåret.</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>74636550</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sjödyn 4,5 km S om Storvreta, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>651412</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6645912</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Vaksala</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2006-05-05</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2006-05-05</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
           <t>Gillis Aronsson</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>Gillis Aronsson</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>16014151</v>
+      </c>
+      <c r="B12" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sjödyns gård, 0,8 km V-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>651566</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6645941</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Vaksala</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2014-04-05</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2014-04-05</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>16014152</v>
+      </c>
+      <c r="B13" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Sjödyns gård, 1,1 km V-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>651271</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6645921</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Vaksala</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2014-04-05</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2014-04-05</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
